--- a/test_import.xlsx
+++ b/test_import.xlsx
@@ -413,50 +413,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asset_name</t>
+          <t>Sl no.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>serial_number</t>
+          <t>EMP ID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>EMPLOYEE NAME</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>MOBILE NUMBER</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Asset NAME</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SERIAL NUMBER</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MODEL NAME</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>INVOICE NUMBER</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>INVOICE DATE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>WARRANTY DATE</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Charger Serial Number</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Old User</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Old Device</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Test Asset Import</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TEST-IMP-001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Test Laptop 123</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Available</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TEST-SN-001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dell XPS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>INV-TEST-001</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Test import</t>
         </is>
       </c>
     </row>
